--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136967139</v>
+        <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583954</v>
+        <v>583913</v>
       </c>
       <c r="R3" t="n">
-        <v>7048375</v>
+        <v>7048371</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,24 +887,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967139</t>
+          <t>https://artportalen.se/Sighting/136966600</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136966600</v>
+        <v>136967043</v>
       </c>
       <c r="B4" t="n">
         <v>93411</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583913</v>
+        <v>583977</v>
       </c>
       <c r="R4" t="n">
-        <v>7048371</v>
+        <v>7048406</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,13 +1010,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136966600</t>
+          <t>https://artportalen.se/Sighting/136967043</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136967043</v>
+        <v>136967161</v>
       </c>
       <c r="B5" t="n">
         <v>93411</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583977</v>
+        <v>583950</v>
       </c>
       <c r="R5" t="n">
-        <v>7048406</v>
+        <v>7048371</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,13 +1122,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967043</t>
+          <t>https://artportalen.se/Sighting/136967161</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136967161</v>
+        <v>136967640</v>
       </c>
       <c r="B6" t="n">
         <v>93411</v>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583950</v>
+        <v>583941</v>
       </c>
       <c r="R6" t="n">
-        <v>7048371</v>
+        <v>7048330</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Ramsele</t>
+          <t>Ådals-Liden</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,65 +1223,74 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967161</t>
+          <t>https://artportalen.se/Sighting/136967640</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136967640</v>
+        <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583941</v>
+        <v>583958</v>
       </c>
       <c r="R7" t="n">
-        <v>7048330</v>
+        <v>7048391</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1309,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Ådals-Liden</t>
+          <t>Ramsele</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,71 +1344,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967640</t>
+          <t>https://artportalen.se/Sighting/136967189</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136967189</v>
+        <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583958</v>
+        <v>583931</v>
       </c>
       <c r="R8" t="n">
-        <v>7048391</v>
+        <v>7048398</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,54 +1467,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967189</t>
+          <t>https://artportalen.se/Sighting/136966943</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136966943</v>
+        <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583931</v>
+        <v>583880</v>
       </c>
       <c r="R9" t="n">
-        <v>7048398</v>
+        <v>7048326</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,24 +1568,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136966943</t>
+          <t>https://artportalen.se/Sighting/136966314</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136966314</v>
+        <v>136966740</v>
       </c>
       <c r="B10" t="n">
         <v>79476</v>
@@ -1616,14 +1616,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583880</v>
+        <v>583903</v>
       </c>
       <c r="R10" t="n">
-        <v>7048326</v>
+        <v>7048368</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,13 +1691,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136966314</t>
+          <t>https://artportalen.se/Sighting/136966740</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136966740</v>
+        <v>136967317</v>
       </c>
       <c r="B11" t="n">
         <v>79476</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583903</v>
+        <v>583962</v>
       </c>
       <c r="R11" t="n">
-        <v>7048368</v>
+        <v>7048367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,13 +1803,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136966740</t>
+          <t>https://artportalen.se/Sighting/136967317</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136967317</v>
+        <v>136967714</v>
       </c>
       <c r="B12" t="n">
         <v>79476</v>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583962</v>
+        <v>583922</v>
       </c>
       <c r="R12" t="n">
-        <v>7048367</v>
+        <v>7048347</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,13 +1915,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967317</t>
+          <t>https://artportalen.se/Sighting/136967714</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136967714</v>
+        <v>136967906</v>
       </c>
       <c r="B13" t="n">
         <v>79476</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583922</v>
+        <v>583911</v>
       </c>
       <c r="R13" t="n">
-        <v>7048347</v>
+        <v>7048325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,13 +2027,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967714</t>
+          <t>https://artportalen.se/Sighting/136967906</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136967906</v>
+        <v>136968082</v>
       </c>
       <c r="B14" t="n">
         <v>79476</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583911</v>
+        <v>583907</v>
       </c>
       <c r="R14" t="n">
-        <v>7048325</v>
+        <v>7048295</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Ramsele</t>
+          <t>Ådals-Liden</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,38 +2139,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967906</t>
+          <t>https://artportalen.se/Sighting/136968082</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136968082</v>
+        <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>80095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583907</v>
+        <v>583963</v>
       </c>
       <c r="R15" t="n">
-        <v>7048295</v>
+        <v>7048349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,13 +2251,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968082</t>
+          <t>https://artportalen.se/Sighting/136967503</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136967503</v>
+        <v>136968145</v>
       </c>
       <c r="B16" t="n">
         <v>80095</v>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583963</v>
+        <v>583907</v>
       </c>
       <c r="R16" t="n">
-        <v>7048349</v>
+        <v>7048291</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,54 +2363,59 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967503</t>
+          <t>https://artportalen.se/Sighting/136968145</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136968145</v>
+        <v>136966325</v>
       </c>
       <c r="B17" t="n">
-        <v>80095</v>
+        <v>58005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583907</v>
+        <v>583867</v>
       </c>
       <c r="R17" t="n">
-        <v>7048291</v>
+        <v>7048324</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,7 +2434,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Ådals-Liden</t>
+          <t>Ramsele</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2439,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,44 +2469,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968145</t>
+          <t>https://artportalen.se/Sighting/136966325</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136966325</v>
+        <v>136966479</v>
       </c>
       <c r="B18" t="n">
-        <v>58005</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583867</v>
+        <v>583895</v>
       </c>
       <c r="R18" t="n">
-        <v>7048324</v>
+        <v>7048359</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2566,7 +2571,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,16 +2602,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136966325</t>
+          <t>https://artportalen.se/Sighting/136966479</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136966479</v>
+        <v>136967765</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,27 +2619,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2638,13 +2657,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583895</v>
+        <v>583908</v>
       </c>
       <c r="R19" t="n">
-        <v>7048359</v>
+        <v>7048345</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2673,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,12 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,64 +2717,59 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136966479</t>
+          <t>https://artportalen.se/Sighting/136967765</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136967765</v>
+        <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>58169</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2769,13 +2778,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583908</v>
+        <v>583909</v>
       </c>
       <c r="R20" t="n">
-        <v>7048345</v>
+        <v>7048305</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2804,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,24 +2838,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136967765</t>
+          <t>https://artportalen.se/Sighting/136967917</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136967917</v>
+        <v>136967937</v>
       </c>
       <c r="B21" t="n">
         <v>99353</v>
@@ -2879,24 +2888,19 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583909</v>
+        <v>583912</v>
       </c>
       <c r="R21" t="n">
-        <v>7048305</v>
+        <v>7048323</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,7 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,132 +2954,16 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136967917</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>136967937</v>
-      </c>
-      <c r="B22" t="n">
-        <v>99353</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>583912</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7048323</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136967937</t>
         </is>
@@ -3103,7 +2991,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136966325</v>
       </c>
       <c r="B17" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136966479</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>136967765</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136966325</v>
       </c>
       <c r="B17" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136966479</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>136967765</v>
       </c>
       <c r="B19" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -2398,11 +2398,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
@@ -2515,11 +2511,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>
@@ -2641,16 +2633,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skumsåstjärnen, Skumsåstjärnen, Ång</t>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136966325</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136966479</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>136967765</v>
       </c>
       <c r="B19" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136966325</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136966479</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>136967765</v>
       </c>
       <c r="B19" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136966325</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136966479</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>136967765</v>
       </c>
       <c r="B19" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83403</v>
+        <v>83404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31934-2026 artfynd.xlsx
+++ b/artfynd/A 31934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136966168</v>
       </c>
       <c r="B2" t="n">
-        <v>83404</v>
+        <v>83407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136966600</v>
       </c>
       <c r="B3" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136967043</v>
       </c>
       <c r="B4" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136967161</v>
       </c>
       <c r="B5" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136967640</v>
       </c>
       <c r="B6" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136967189</v>
       </c>
       <c r="B7" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>136966943</v>
       </c>
       <c r="B8" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136966314</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136966740</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>136967317</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>136967714</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136967906</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>136968082</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136967503</v>
       </c>
       <c r="B15" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136968145</v>
       </c>
       <c r="B16" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136966325</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136966479</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>136967765</v>
       </c>
       <c r="B19" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136967917</v>
       </c>
       <c r="B20" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>136967937</v>
       </c>
       <c r="B21" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
